--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -9,14 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
-    <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
-    <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +82,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping du modèle métier Opérateur de saisie entre CDA et FHIR.</t>
+    <t>Ce ConceptMap présente deux groupes de mapping :
+ - Groupe Mapping 1 : entre le modèle logique métier de l'opérateur de saisieet et l'élément CDA dataEnterer
+ - Groupe Mapping 2 : entre l'élément CDA dataEnterer et DataEntererExtension en FHIR</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -129,115 +129,16 @@
     <t>dataEnterer.time</t>
   </si>
   <si>
-    <t>OperateurSaisie.operateurSaisie</t>
+    <t>OperateurSaisie.operateurSaisie[PersonneStructure]</t>
   </si>
   <si>
     <t>dataEnterer.assignedEntity</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PersonneStructure</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity</t>
-  </si>
-  <si>
-    <t>PersonneStructure</t>
-  </si>
-  <si>
-    <t>assignedEntity</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.identifiantPersonne</t>
-  </si>
-  <si>
-    <t>assignedEntity.id</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.professionRole</t>
-  </si>
-  <si>
-    <t>assignedEntity.code</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.adresse</t>
-  </si>
-  <si>
-    <t>assignedEntity.addr</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t>assignedEntity.telecom</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.IdentitePersonne</t>
-  </si>
-  <si>
-    <t>assignedEntity.assignedPerson</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.IdentitePersonne.nomPersonne</t>
-  </si>
-  <si>
-    <t>assignedEntity.assignedPerson.name.family</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.IdentitePersonne.nomPersonne.prenomPersonne</t>
-  </si>
-  <si>
-    <t>assignedEntity.assignedPerson.name.given</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.IdentitePersonne.civilite</t>
-  </si>
-  <si>
-    <t>assignedEntity.assignedPerson.prefix</t>
-  </si>
-  <si>
-    <t>PersonneStructure.personne.IdentitePersonne.titre</t>
-  </si>
-  <si>
-    <t>assignedEntity.assignedPerson.suffix</t>
-  </si>
-  <si>
-    <t>PersonneStructure.structure</t>
-  </si>
-  <si>
-    <t>assignedEntity.representedOrganization</t>
-  </si>
-  <si>
-    <t>PersonneStructure.structure.identifiantStructure</t>
-  </si>
-  <si>
-    <t>assignedEntity.representedOrganization.id</t>
-  </si>
-  <si>
-    <t>PersonneStructure.structure.nomStructure</t>
-  </si>
-  <si>
-    <t>assignedEntity.representedOrganization.name</t>
-  </si>
-  <si>
-    <t>PersonneStructure.structure.adresse</t>
-  </si>
-  <si>
-    <t>assignedEntity.representedOrganization.addr</t>
-  </si>
-  <si>
-    <t>PersonneStructure.structure.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t>assignedEntity.representedOrganization.telecom</t>
-  </si>
-  <si>
-    <t>PersonneStructure.structure.secteurActivite</t>
-  </si>
-  <si>
-    <t>assignedEntity.representedOrganization.standardIndustryClassCode</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-data-enterer-extension</t>
+  </si>
+  <si>
+    <t>DataEntererExtension</t>
   </si>
   <si>
     <t>DataEntererExtension.extension:time</t>
@@ -582,7 +483,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -604,7 +505,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>30</v>
@@ -613,7 +514,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>30</v>
@@ -621,325 +522,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E3" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mapping du modèle métier Opérateur de saisie : CDA et FHIR</t>
+    <t>Mapping du modèle métier Opérateur de saisie/CDA/FHIR</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,8 +83,8 @@
   </si>
   <si>
     <t>Ce ConceptMap présente deux groupes de mapping :
- - Groupe Mapping 1 : entre le modèle logique métier de l'opérateur de saisieet et l'élément CDA dataEnterer
- - Groupe Mapping 2 : entre l'élément CDA dataEnterer et DataEntererExtension en FHIR</t>
+ - Groupe Mapping 1 : entre le modèle logique métier de l'opérateur de saisie et l'élément CDA dataEnterer
+ - Groupe Mapping 2 : entre l'élément CDA dataEnterer et l'extension FHIR DataEntererExtension</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -129,13 +129,13 @@
     <t>dataEnterer.time</t>
   </si>
   <si>
-    <t>OperateurSaisie.operateurSaisie[PersonneStructure]</t>
+    <t>OperateurSaisie.operateurSaisie</t>
   </si>
   <si>
     <t>dataEnterer.assignedEntity</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-data-enterer-extension</t>
+    <t>http://hl7.org/fhir/uv/fhir-clinical-document/StructureDefinition/data-enterer-extension</t>
   </si>
   <si>
     <t>DataEntererExtension</t>
@@ -144,7 +144,7 @@
     <t>DataEntererExtension.extension:time</t>
   </si>
   <si>
-    <t>DataEntererExtension.extension:party</t>
+    <t>DataEntererExtension.extension:party.ValueReference</t>
   </si>
 </sst>
 </file>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
